--- a/visual_model/data/230521班综合测评计算表格模板.xlsx
+++ b/visual_model/data/230521班综合测评计算表格模板.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PaddleOCR\visual_model\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54DB7D35-860E-4144-96A3-06113E33B13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="20" windowWidth="25580" windowHeight="15260" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="25580" windowHeight="15260" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="综合测评计算表" sheetId="1" r:id="rId1"/>
     <sheet name="加减分说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">综合测评计算表!$A$3:$S$85</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">综合测评计算表!$A$3:$S$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>专业</t>
   </si>
@@ -115,102 +114,126 @@
   <si>
     <t>班级测评小组组长签名</t>
   </si>
+  <si>
+    <t>A3—扣分项</t>
+  </si>
+  <si>
+    <t>思想道德素质(A)总分%</t>
+  </si>
+  <si>
+    <t>学习成绩%</t>
+  </si>
+  <si>
+    <t>C1—科技竞赛项目</t>
+  </si>
+  <si>
+    <t>素质拓展(C)总分</t>
+  </si>
+  <si>
+    <t>素质拓展(C)总分10%</t>
+  </si>
+  <si>
+    <t>综合测评总成绩8%</t>
+  </si>
+  <si>
+    <t>学生签字</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="楷体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="28"/>
-      <color theme="1"/>
       <name val="华文行楷"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="28"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
       <name val="楷体"/>
       <charset val="134"/>
+      <color indexed="8"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Arial"/>
       <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="16"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -235,42 +258,42 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right/>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
@@ -292,26 +315,26 @@
     <border>
       <left/>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
@@ -324,14 +347,14 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
+        <color auto="true"/>
       </bottom>
       <diagonal/>
     </border>
@@ -347,107 +370,107 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9"/>
   </cellStyleXfs>
   <cellXfs count="39">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment wrapText="true"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -460,7 +483,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -747,28 +770,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:Y95"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="5.6328125" style="30" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.26953125" style="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.26953125" style="30" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.26953125" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="30" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="7.81640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="8.90625" style="30"/>
-    <col min="11" max="13" width="7.81640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.6328125" style="30" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="7.81640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="8.90625" style="30"/>
-    <col min="19" max="19" width="7.81640625" style="30" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.6328125" style="30" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="8.90625" style="30"/>
+    <col bestFit="true" customWidth="true" max="1" min="1" style="30" width="5.6328125"/>
+    <col bestFit="true" customWidth="true" max="2" min="2" style="30" width="9.26953125"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" style="30" width="7.26953125"/>
+    <col bestFit="true" customWidth="true" max="4" min="4" style="31" width="7.26953125"/>
+    <col bestFit="true" customWidth="true" max="5" min="5" style="30" width="13.54296875"/>
+    <col bestFit="true" customWidth="true" max="8" min="6" style="30" width="7.81640625"/>
+    <col max="10" min="9" style="30" width="8.90625"/>
+    <col bestFit="true" customWidth="true" max="13" min="11" style="30" width="7.81640625"/>
+    <col bestFit="true" customWidth="true" max="14" min="14" style="30" width="5.6328125"/>
+    <col bestFit="true" customWidth="true" max="16" min="15" style="30" width="7.81640625"/>
+    <col max="18" min="17" style="30" width="8.90625"/>
+    <col bestFit="true" customWidth="true" max="19" min="19" style="30" width="7.81640625"/>
+    <col bestFit="true" customWidth="true" max="20" min="20" style="30" width="5.6328125"/>
+    <col max="25" min="21" style="30" width="8.90625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="56.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="56.5" customHeight="true">
       <c r="A1" s="37" t="s">
         <v>10</v>
       </c>
@@ -792,7 +815,7 @@
       <c r="S1" s="37"/>
       <c r="T1" s="37"/>
     </row>
-    <row r="2" spans="1:21" ht="26.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="26.15" customHeight="true">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -820,7 +843,7 @@
       <c r="S2" s="1"/>
       <c r="T2" s="12"/>
     </row>
-    <row r="3" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="60">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -843,46 +866,49 @@
         <v>4</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>16</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="L3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="N3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="R3" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="S3" s="14" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="U3" s="30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15">
       <c r="A4" s="1"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4"/>
@@ -905,7 +931,7 @@
       <c r="T4" s="21"/>
       <c r="U4" s="22"/>
     </row>
-    <row r="5" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="15">
       <c r="A5" s="1"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4"/>
@@ -928,7 +954,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="22"/>
     </row>
-    <row r="6" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="15">
       <c r="A6" s="1"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
@@ -951,7 +977,7 @@
       <c r="T6" s="21"/>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="15">
       <c r="A7" s="1"/>
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
@@ -974,7 +1000,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="15">
       <c r="A8" s="1"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4"/>
@@ -997,7 +1023,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="22"/>
     </row>
-    <row r="9" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="15">
       <c r="A9" s="1"/>
       <c r="B9" s="3"/>
       <c r="C9" s="4"/>
@@ -1020,7 +1046,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="15">
       <c r="A10" s="1"/>
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
@@ -1043,7 +1069,7 @@
       <c r="T10" s="21"/>
       <c r="U10" s="22"/>
     </row>
-    <row r="11" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="15">
       <c r="A11" s="1"/>
       <c r="B11" s="3"/>
       <c r="C11" s="4"/>
@@ -1066,7 +1092,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="22"/>
     </row>
-    <row r="12" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="15">
       <c r="A12" s="1"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4"/>
@@ -1089,7 +1115,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="15">
       <c r="A13" s="1"/>
       <c r="B13" s="3"/>
       <c r="C13" s="4"/>
@@ -1112,7 +1138,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="22"/>
     </row>
-    <row r="14" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="15">
       <c r="A14" s="1"/>
       <c r="B14" s="3"/>
       <c r="C14" s="4"/>
@@ -1135,7 +1161,7 @@
       <c r="T14" s="21"/>
       <c r="U14" s="22"/>
     </row>
-    <row r="15" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="15">
       <c r="A15" s="1"/>
       <c r="B15" s="3"/>
       <c r="C15" s="4"/>
@@ -1158,7 +1184,7 @@
       <c r="T15" s="21"/>
       <c r="U15" s="22"/>
     </row>
-    <row r="16" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="15">
       <c r="A16" s="1"/>
       <c r="B16" s="3"/>
       <c r="C16" s="4"/>
@@ -1181,7 +1207,7 @@
       <c r="T16" s="21"/>
       <c r="U16" s="22"/>
     </row>
-    <row r="17" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="15">
       <c r="A17" s="1"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
@@ -1204,7 +1230,7 @@
       <c r="T17" s="21"/>
       <c r="U17" s="22"/>
     </row>
-    <row r="18" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="15">
       <c r="A18" s="1"/>
       <c r="B18" s="3"/>
       <c r="C18" s="4"/>
@@ -1227,7 +1253,7 @@
       <c r="T18" s="21"/>
       <c r="U18" s="22"/>
     </row>
-    <row r="19" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="15">
       <c r="A19" s="1"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
@@ -1250,7 +1276,7 @@
       <c r="T19" s="21"/>
       <c r="U19" s="22"/>
     </row>
-    <row r="20" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" ht="15">
       <c r="A20" s="1"/>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
@@ -1273,7 +1299,7 @@
       <c r="T20" s="21"/>
       <c r="U20" s="22"/>
     </row>
-    <row r="21" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="15">
       <c r="A21" s="1"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
@@ -1296,7 +1322,7 @@
       <c r="T21" s="21"/>
       <c r="U21" s="22"/>
     </row>
-    <row r="22" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="15">
       <c r="A22" s="1"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
@@ -1319,7 +1345,7 @@
       <c r="T22" s="21"/>
       <c r="U22" s="22"/>
     </row>
-    <row r="23" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="15">
       <c r="A23" s="1"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
@@ -1342,7 +1368,7 @@
       <c r="T23" s="21"/>
       <c r="U23" s="22"/>
     </row>
-    <row r="24" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" ht="15">
       <c r="A24" s="1"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
@@ -1365,7 +1391,7 @@
       <c r="T24" s="21"/>
       <c r="U24" s="22"/>
     </row>
-    <row r="25" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" ht="15">
       <c r="A25" s="1"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
@@ -1388,7 +1414,7 @@
       <c r="T25" s="21"/>
       <c r="U25" s="22"/>
     </row>
-    <row r="26" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" ht="15">
       <c r="A26" s="1"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
@@ -1411,7 +1437,7 @@
       <c r="T26" s="21"/>
       <c r="U26" s="22"/>
     </row>
-    <row r="27" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" ht="15">
       <c r="A27" s="1"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
@@ -1434,7 +1460,7 @@
       <c r="T27" s="21"/>
       <c r="U27" s="22"/>
     </row>
-    <row r="28" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" ht="15">
       <c r="A28" s="1"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
@@ -1457,7 +1483,7 @@
       <c r="T28" s="21"/>
       <c r="U28" s="22"/>
     </row>
-    <row r="29" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" ht="15">
       <c r="A29" s="1"/>
       <c r="B29" s="3"/>
       <c r="C29" s="4"/>
@@ -1480,7 +1506,7 @@
       <c r="T29" s="21"/>
       <c r="U29" s="22"/>
     </row>
-    <row r="30" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="15">
       <c r="A30" s="1"/>
       <c r="B30" s="3"/>
       <c r="C30" s="4"/>
@@ -1503,7 +1529,7 @@
       <c r="T30" s="21"/>
       <c r="U30" s="22"/>
     </row>
-    <row r="31" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" ht="15">
       <c r="A31" s="1"/>
       <c r="B31" s="3"/>
       <c r="C31" s="4"/>
@@ -1526,7 +1552,7 @@
       <c r="T31" s="21"/>
       <c r="U31" s="22"/>
     </row>
-    <row r="32" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="15">
       <c r="A32" s="1"/>
       <c r="B32" s="3"/>
       <c r="C32" s="4"/>
@@ -1549,7 +1575,7 @@
       <c r="T32" s="21"/>
       <c r="U32" s="22"/>
     </row>
-    <row r="33" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" ht="15">
       <c r="A33" s="1"/>
       <c r="B33" s="3"/>
       <c r="C33" s="4"/>
@@ -1572,7 +1598,7 @@
       <c r="T33" s="21"/>
       <c r="U33" s="22"/>
     </row>
-    <row r="34" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" ht="15">
       <c r="A34" s="1"/>
       <c r="B34" s="3"/>
       <c r="C34" s="4"/>
@@ -1595,7 +1621,7 @@
       <c r="T34" s="21"/>
       <c r="U34" s="22"/>
     </row>
-    <row r="35" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="15">
       <c r="A35" s="1"/>
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
@@ -1617,7 +1643,7 @@
       <c r="S35" s="20"/>
       <c r="T35" s="21"/>
     </row>
-    <row r="36" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" ht="15">
       <c r="A36" s="1"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1639,7 +1665,7 @@
       <c r="S36" s="4"/>
       <c r="T36" s="27"/>
     </row>
-    <row r="37" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="15">
       <c r="A37" s="1"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1661,7 +1687,7 @@
       <c r="S37" s="4"/>
       <c r="T37" s="12"/>
     </row>
-    <row r="38" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" ht="15">
       <c r="A38" s="1"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1683,7 +1709,7 @@
       <c r="S38" s="4"/>
       <c r="T38" s="12"/>
     </row>
-    <row r="39" spans="1:21" s="29" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" s="29" customFormat="true" ht="15">
       <c r="A39" s="1"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1705,7 +1731,7 @@
       <c r="S39" s="4"/>
       <c r="T39" s="28"/>
     </row>
-    <row r="40" spans="1:21" s="29" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" s="29" customFormat="true" ht="15">
       <c r="A40" s="1">
         <v>37</v>
       </c>
@@ -1729,7 +1755,7 @@
       <c r="S40" s="4"/>
       <c r="T40" s="28"/>
     </row>
-    <row r="41" spans="1:21" s="29" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" s="29" customFormat="true" ht="15">
       <c r="A41" s="1">
         <v>38</v>
       </c>
@@ -1753,7 +1779,7 @@
       <c r="S41" s="4"/>
       <c r="T41" s="28"/>
     </row>
-    <row r="42" spans="1:21" s="29" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" s="29" customFormat="true" ht="15">
       <c r="A42" s="1">
         <v>39</v>
       </c>
@@ -1777,7 +1803,7 @@
       <c r="S42" s="4"/>
       <c r="T42" s="28"/>
     </row>
-    <row r="43" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" ht="15">
       <c r="A43" s="1">
         <v>40</v>
       </c>
@@ -1801,7 +1827,7 @@
       <c r="S43" s="4"/>
       <c r="T43" s="12"/>
     </row>
-    <row r="44" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" ht="15">
       <c r="A44" s="1">
         <v>41</v>
       </c>
@@ -1825,7 +1851,7 @@
       <c r="S44" s="4"/>
       <c r="T44" s="12"/>
     </row>
-    <row r="45" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" ht="15">
       <c r="A45" s="1">
         <v>42</v>
       </c>
@@ -1849,7 +1875,7 @@
       <c r="S45" s="4"/>
       <c r="T45" s="12"/>
     </row>
-    <row r="46" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" ht="15">
       <c r="A46" s="1">
         <v>43</v>
       </c>
@@ -1873,7 +1899,7 @@
       <c r="S46" s="4"/>
       <c r="T46" s="12"/>
     </row>
-    <row r="47" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" ht="15">
       <c r="A47" s="1">
         <v>44</v>
       </c>
@@ -1897,7 +1923,7 @@
       <c r="S47" s="4"/>
       <c r="T47" s="12"/>
     </row>
-    <row r="48" spans="1:21" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" ht="15">
       <c r="A48" s="1">
         <v>45</v>
       </c>
@@ -1921,7 +1947,7 @@
       <c r="S48" s="4"/>
       <c r="T48" s="12"/>
     </row>
-    <row r="49" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" ht="15">
       <c r="A49" s="1">
         <v>46</v>
       </c>
@@ -1945,7 +1971,7 @@
       <c r="S49" s="4"/>
       <c r="T49" s="12"/>
     </row>
-    <row r="50" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" ht="15">
       <c r="A50" s="1">
         <v>47</v>
       </c>
@@ -1969,7 +1995,7 @@
       <c r="S50" s="4"/>
       <c r="T50" s="12"/>
     </row>
-    <row r="51" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" ht="15">
       <c r="A51" s="1">
         <v>48</v>
       </c>
@@ -1993,7 +2019,7 @@
       <c r="S51" s="4"/>
       <c r="T51" s="12"/>
     </row>
-    <row r="52" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:20" ht="15">
       <c r="A52" s="1">
         <v>49</v>
       </c>
@@ -2017,7 +2043,7 @@
       <c r="S52" s="4"/>
       <c r="T52" s="12"/>
     </row>
-    <row r="53" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:20" ht="15">
       <c r="A53" s="1">
         <v>50</v>
       </c>
@@ -2041,7 +2067,7 @@
       <c r="S53" s="4"/>
       <c r="T53" s="12"/>
     </row>
-    <row r="54" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:20" ht="15">
       <c r="A54" s="1">
         <v>51</v>
       </c>
@@ -2065,7 +2091,7 @@
       <c r="S54" s="4"/>
       <c r="T54" s="12"/>
     </row>
-    <row r="55" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:20" ht="15">
       <c r="A55" s="1">
         <v>52</v>
       </c>
@@ -2089,7 +2115,7 @@
       <c r="S55" s="4"/>
       <c r="T55" s="12"/>
     </row>
-    <row r="56" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:20" ht="15">
       <c r="A56" s="1">
         <v>53</v>
       </c>
@@ -2113,7 +2139,7 @@
       <c r="S56" s="4"/>
       <c r="T56" s="12"/>
     </row>
-    <row r="57" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:20" ht="15">
       <c r="A57" s="1">
         <v>54</v>
       </c>
@@ -2137,7 +2163,7 @@
       <c r="S57" s="4"/>
       <c r="T57" s="12"/>
     </row>
-    <row r="58" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:20" ht="15">
       <c r="A58" s="1">
         <v>55</v>
       </c>
@@ -2161,7 +2187,7 @@
       <c r="S58" s="4"/>
       <c r="T58" s="12"/>
     </row>
-    <row r="59" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:20" ht="15">
       <c r="A59" s="1">
         <v>56</v>
       </c>
@@ -2185,7 +2211,7 @@
       <c r="S59" s="4"/>
       <c r="T59" s="12"/>
     </row>
-    <row r="60" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:20" ht="15">
       <c r="A60" s="1">
         <v>57</v>
       </c>
@@ -2209,7 +2235,7 @@
       <c r="S60" s="4"/>
       <c r="T60" s="12"/>
     </row>
-    <row r="61" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:20" ht="15">
       <c r="A61" s="1">
         <v>58</v>
       </c>
@@ -2233,7 +2259,7 @@
       <c r="S61" s="4"/>
       <c r="T61" s="12"/>
     </row>
-    <row r="62" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:20" ht="15">
       <c r="A62" s="1">
         <v>59</v>
       </c>
@@ -2257,7 +2283,7 @@
       <c r="S62" s="4"/>
       <c r="T62" s="12"/>
     </row>
-    <row r="63" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:20" ht="15">
       <c r="A63" s="1">
         <v>60</v>
       </c>
@@ -2281,7 +2307,7 @@
       <c r="S63" s="4"/>
       <c r="T63" s="12"/>
     </row>
-    <row r="64" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:20" ht="15">
       <c r="A64" s="1">
         <v>61</v>
       </c>
@@ -2305,7 +2331,7 @@
       <c r="S64" s="4"/>
       <c r="T64" s="12"/>
     </row>
-    <row r="65" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" ht="15">
       <c r="A65" s="1">
         <v>62</v>
       </c>
@@ -2329,7 +2355,7 @@
       <c r="S65" s="4"/>
       <c r="T65" s="12"/>
     </row>
-    <row r="66" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" ht="15">
       <c r="A66" s="1">
         <v>63</v>
       </c>
@@ -2353,7 +2379,7 @@
       <c r="S66" s="4"/>
       <c r="T66" s="12"/>
     </row>
-    <row r="67" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" ht="15">
       <c r="A67" s="1">
         <v>64</v>
       </c>
@@ -2377,7 +2403,7 @@
       <c r="S67" s="4"/>
       <c r="T67" s="12"/>
     </row>
-    <row r="68" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" ht="15">
       <c r="A68" s="1">
         <v>65</v>
       </c>
@@ -2401,7 +2427,7 @@
       <c r="S68" s="4"/>
       <c r="T68" s="12"/>
     </row>
-    <row r="69" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" ht="15">
       <c r="A69" s="1">
         <v>66</v>
       </c>
@@ -2425,7 +2451,7 @@
       <c r="S69" s="4"/>
       <c r="T69" s="12"/>
     </row>
-    <row r="70" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" ht="15">
       <c r="A70" s="1">
         <v>67</v>
       </c>
@@ -2449,7 +2475,7 @@
       <c r="S70" s="4"/>
       <c r="T70" s="12"/>
     </row>
-    <row r="71" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" ht="15">
       <c r="A71" s="1">
         <v>68</v>
       </c>
@@ -2473,7 +2499,7 @@
       <c r="S71" s="4"/>
       <c r="T71" s="12"/>
     </row>
-    <row r="72" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:20" ht="15">
       <c r="A72" s="1">
         <v>69</v>
       </c>
@@ -2497,7 +2523,7 @@
       <c r="S72" s="4"/>
       <c r="T72" s="12"/>
     </row>
-    <row r="73" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:20" ht="15">
       <c r="A73" s="1">
         <v>70</v>
       </c>
@@ -2521,7 +2547,7 @@
       <c r="S73" s="4"/>
       <c r="T73" s="12"/>
     </row>
-    <row r="74" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:20" ht="15">
       <c r="A74" s="1">
         <v>71</v>
       </c>
@@ -2545,7 +2571,7 @@
       <c r="S74" s="4"/>
       <c r="T74" s="12"/>
     </row>
-    <row r="75" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:20" ht="15">
       <c r="A75" s="1">
         <v>72</v>
       </c>
@@ -2569,7 +2595,7 @@
       <c r="S75" s="4"/>
       <c r="T75" s="12"/>
     </row>
-    <row r="76" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:20" ht="15">
       <c r="A76" s="1">
         <v>73</v>
       </c>
@@ -2593,7 +2619,7 @@
       <c r="S76" s="4"/>
       <c r="T76" s="12"/>
     </row>
-    <row r="77" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:20" ht="15">
       <c r="A77" s="1">
         <v>74</v>
       </c>
@@ -2617,7 +2643,7 @@
       <c r="S77" s="4"/>
       <c r="T77" s="12"/>
     </row>
-    <row r="78" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:20" ht="15">
       <c r="A78" s="1">
         <v>75</v>
       </c>
@@ -2641,7 +2667,7 @@
       <c r="S78" s="4"/>
       <c r="T78" s="12"/>
     </row>
-    <row r="79" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:20" ht="15">
       <c r="A79" s="1">
         <v>76</v>
       </c>
@@ -2665,7 +2691,7 @@
       <c r="S79" s="4"/>
       <c r="T79" s="12"/>
     </row>
-    <row r="80" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:20" ht="15">
       <c r="A80" s="1">
         <v>77</v>
       </c>
@@ -2689,7 +2715,7 @@
       <c r="S80" s="4"/>
       <c r="T80" s="12"/>
     </row>
-    <row r="81" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="15">
       <c r="A81" s="1">
         <v>78</v>
       </c>
@@ -2713,7 +2739,7 @@
       <c r="S81" s="4"/>
       <c r="T81" s="12"/>
     </row>
-    <row r="82" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="15">
       <c r="A82" s="1">
         <v>79</v>
       </c>
@@ -2737,7 +2763,7 @@
       <c r="S82" s="4"/>
       <c r="T82" s="12"/>
     </row>
-    <row r="83" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="15">
       <c r="A83" s="1">
         <v>80</v>
       </c>
@@ -2761,7 +2787,7 @@
       <c r="S83" s="4"/>
       <c r="T83" s="12"/>
     </row>
-    <row r="84" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="15">
       <c r="A84" s="1">
         <v>81</v>
       </c>
@@ -2785,7 +2811,7 @@
       <c r="S84" s="4"/>
       <c r="T84" s="12"/>
     </row>
-    <row r="85" spans="1:20" ht="15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="15">
       <c r="A85" s="1">
         <v>82</v>
       </c>
@@ -2809,7 +2835,7 @@
       <c r="S85" s="4"/>
       <c r="T85" s="12"/>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20">
       <c r="A86" s="34" t="s">
         <v>24</v>
       </c>
@@ -2833,7 +2859,7 @@
       <c r="S86" s="36"/>
       <c r="T86" s="36"/>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20">
       <c r="A87" s="35"/>
       <c r="B87" s="35"/>
       <c r="C87" s="35"/>
@@ -2855,7 +2881,7 @@
       <c r="S87" s="36"/>
       <c r="T87" s="36"/>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20">
       <c r="A88" s="35"/>
       <c r="B88" s="35"/>
       <c r="C88" s="35"/>
@@ -2877,7 +2903,7 @@
       <c r="S88" s="36"/>
       <c r="T88" s="36"/>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20">
       <c r="A89" s="35"/>
       <c r="B89" s="35"/>
       <c r="C89" s="35"/>
@@ -2899,7 +2925,7 @@
       <c r="S89" s="36"/>
       <c r="T89" s="36"/>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20">
       <c r="A90" s="35"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35"/>
@@ -2921,7 +2947,7 @@
       <c r="S90" s="36"/>
       <c r="T90" s="36"/>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20">
       <c r="A91" s="34" t="s">
         <v>25</v>
       </c>
@@ -2945,7 +2971,7 @@
       <c r="S91" s="36"/>
       <c r="T91" s="36"/>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20">
       <c r="A92" s="35"/>
       <c r="B92" s="35"/>
       <c r="C92" s="35"/>
@@ -2967,7 +2993,7 @@
       <c r="S92" s="36"/>
       <c r="T92" s="36"/>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20">
       <c r="A93" s="35"/>
       <c r="B93" s="35"/>
       <c r="C93" s="35"/>
@@ -2989,7 +3015,7 @@
       <c r="S93" s="36"/>
       <c r="T93" s="36"/>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20">
       <c r="A94" s="35"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35"/>
@@ -3011,7 +3037,7 @@
       <c r="S94" s="36"/>
       <c r="T94" s="36"/>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20">
       <c r="A95" s="35"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35"/>
@@ -3034,8 +3060,8 @@
       <c r="T95" s="36"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S95" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="D4:S35">
+  <autoFilter ref="A3:S95"/>
+  <sortState ref="D4:S35">
     <sortCondition descending="1" ref="S4:S35"/>
   </sortState>
   <mergeCells count="8">
@@ -3049,25 +3075,25 @@
     <mergeCell ref="A86:D90"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
-  <pageMargins left="0.70069400000000004" right="0.70069400000000004" top="0.75138899999999997" bottom="0.75138899999999997" header="0.29861100000000002" footer="0.29861100000000002"/>
-  <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="landscape"/>
+  <pageMargins left="0.700694" right="0.700694" top="0.751389" bottom="0.751389" header="0.298611" footer="0.298611"/>
+  <pageSetup fitToHeight="0" orientation="landscape" paperSize="9" scale="73"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J83"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="7.7265625" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" customWidth="1"/>
-    <col min="4" max="6" width="15.7265625" customWidth="1"/>
-    <col min="7" max="9" width="20.7265625" customWidth="1"/>
-    <col min="10" max="10" width="25.7265625" customWidth="1"/>
+    <col customWidth="true" max="1" min="1" width="7.7265625"/>
+    <col customWidth="true" max="2" min="2" width="16.26953125"/>
+    <col customWidth="true" max="3" min="3" width="16.453125"/>
+    <col customWidth="true" max="6" min="4" width="15.7265625"/>
+    <col customWidth="true" max="9" min="7" width="20.7265625"/>
+    <col customWidth="true" max="10" min="10" width="25.7265625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="22" customHeight="true">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3084,10 +3110,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
@@ -3099,7 +3125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="17.25" customHeight="true">
       <c r="A2" s="3"/>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
@@ -3111,7 +3137,7 @@
       <c r="I2" s="9"/>
       <c r="J2" s="8"/>
     </row>
-    <row r="3" spans="1:10" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="74.25" customHeight="true">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5"/>
@@ -3123,7 +3149,7 @@
       <c r="I3" s="9"/>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" spans="1:10" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="75.75" customHeight="true">
       <c r="A4" s="3"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
@@ -3135,7 +3161,7 @@
       <c r="I4" s="9"/>
       <c r="J4" s="8"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="3"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
@@ -3147,7 +3173,7 @@
       <c r="I5" s="9"/>
       <c r="J5" s="8"/>
     </row>
-    <row r="6" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="45" customHeight="true">
       <c r="A6" s="3"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -3159,7 +3185,7 @@
       <c r="I6" s="9"/>
       <c r="J6" s="8"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" s="3"/>
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
@@ -3171,7 +3197,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="8"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" s="3"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
@@ -3183,7 +3209,7 @@
       <c r="I8" s="9"/>
       <c r="J8" s="8"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9" s="3"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5"/>
@@ -3195,7 +3221,7 @@
       <c r="I9" s="9"/>
       <c r="J9" s="8"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="A10" s="3"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5"/>
@@ -3207,7 +3233,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="A11" s="3"/>
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
@@ -3219,7 +3245,7 @@
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" s="3"/>
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
@@ -3231,7 +3257,7 @@
       <c r="I12" s="9"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
@@ -3243,7 +3269,7 @@
       <c r="I13" s="9"/>
       <c r="J13" s="8"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
@@ -3255,7 +3281,7 @@
       <c r="I14" s="9"/>
       <c r="J14" s="8"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
@@ -3267,7 +3293,7 @@
       <c r="I15" s="9"/>
       <c r="J15" s="8"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" s="3"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
@@ -3279,7 +3305,7 @@
       <c r="I16" s="9"/>
       <c r="J16" s="8"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="3"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
@@ -3291,7 +3317,7 @@
       <c r="I17" s="9"/>
       <c r="J17" s="8"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" s="3"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
@@ -3303,7 +3329,7 @@
       <c r="I18" s="9"/>
       <c r="J18" s="8"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" s="3"/>
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
@@ -3315,7 +3341,7 @@
       <c r="I19" s="9"/>
       <c r="J19" s="8"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" s="3"/>
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
@@ -3327,7 +3353,7 @@
       <c r="I20" s="8"/>
       <c r="J20" s="8"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" s="3"/>
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
@@ -3339,7 +3365,7 @@
       <c r="I21" s="9"/>
       <c r="J21" s="8"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22" s="3"/>
       <c r="B22" s="4"/>
       <c r="C22" s="5"/>
@@ -3351,7 +3377,7 @@
       <c r="I22" s="8"/>
       <c r="J22" s="8"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" s="3"/>
       <c r="B23" s="4"/>
       <c r="C23" s="5"/>
@@ -3363,7 +3389,7 @@
       <c r="I23" s="9"/>
       <c r="J23" s="8"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" s="3"/>
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
@@ -3375,7 +3401,7 @@
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" s="3"/>
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
@@ -3387,7 +3413,7 @@
       <c r="I25" s="8"/>
       <c r="J25" s="8"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" s="3"/>
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
@@ -3399,7 +3425,7 @@
       <c r="I26" s="9"/>
       <c r="J26" s="8"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" s="3"/>
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
@@ -3411,7 +3437,7 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" s="3"/>
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
@@ -3423,7 +3449,7 @@
       <c r="I28" s="9"/>
       <c r="J28" s="8"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" s="3"/>
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
@@ -3435,7 +3461,7 @@
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" s="3"/>
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
@@ -3447,7 +3473,7 @@
       <c r="I30" s="9"/>
       <c r="J30" s="8"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="3"/>
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
@@ -3459,7 +3485,7 @@
       <c r="I31" s="9"/>
       <c r="J31" s="8"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
@@ -3471,7 +3497,7 @@
       <c r="I32" s="9"/>
       <c r="J32" s="8"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="10"/>
@@ -3483,7 +3509,7 @@
       <c r="I33" s="8"/>
       <c r="J33" s="8"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -3495,7 +3521,7 @@
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -3507,7 +3533,7 @@
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -3519,7 +3545,7 @@
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -3531,7 +3557,7 @@
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -3543,7 +3569,7 @@
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -3555,7 +3581,7 @@
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -3567,7 +3593,7 @@
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -3579,7 +3605,7 @@
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -3591,7 +3617,7 @@
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -3603,7 +3629,7 @@
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -3615,7 +3641,7 @@
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -3627,7 +3653,7 @@
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -3639,7 +3665,7 @@
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -3651,7 +3677,7 @@
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -3663,7 +3689,7 @@
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -3675,7 +3701,7 @@
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -3687,7 +3713,7 @@
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -3699,7 +3725,7 @@
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -3711,7 +3737,7 @@
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -3723,7 +3749,7 @@
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -3735,7 +3761,7 @@
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -3747,7 +3773,7 @@
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -3759,7 +3785,7 @@
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -3771,7 +3797,7 @@
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -3783,7 +3809,7 @@
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -3795,7 +3821,7 @@
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -3807,7 +3833,7 @@
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3819,7 +3845,7 @@
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -3831,7 +3857,7 @@
       <c r="I62" s="4"/>
       <c r="J62" s="4"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -3843,7 +3869,7 @@
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -3855,7 +3881,7 @@
       <c r="I64" s="4"/>
       <c r="J64" s="4"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -3867,7 +3893,7 @@
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -3879,7 +3905,7 @@
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -3891,7 +3917,7 @@
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -3903,7 +3929,7 @@
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -3915,7 +3941,7 @@
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -3927,7 +3953,7 @@
       <c r="I70" s="4"/>
       <c r="J70" s="4"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -3939,7 +3965,7 @@
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -3951,7 +3977,7 @@
       <c r="I72" s="4"/>
       <c r="J72" s="4"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -3963,7 +3989,7 @@
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -3975,7 +4001,7 @@
       <c r="I74" s="4"/>
       <c r="J74" s="4"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -3987,7 +4013,7 @@
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -3999,7 +4025,7 @@
       <c r="I76" s="4"/>
       <c r="J76" s="4"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -4011,7 +4037,7 @@
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -4023,7 +4049,7 @@
       <c r="I78" s="4"/>
       <c r="J78" s="4"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -4035,7 +4061,7 @@
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -4047,7 +4073,7 @@
       <c r="I80" s="4"/>
       <c r="J80" s="4"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -4059,7 +4085,7 @@
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -4071,7 +4097,7 @@
       <c r="I82" s="4"/>
       <c r="J82" s="4"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -4085,6 +4111,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
-  <pageMargins left="0.69930599999999998" right="0.69930599999999998" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699306" right="0.699306" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>